--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Not met by the model: 0 - 17% at level 55 whatever the share of forged enchantments, and 0 - 7.5% with the best meal of the ice cream and ramen shops in the best case (its buffs at the start of the fight, 40 battles, 2026-10-09). What a player at 55 adds beyond the model (unique pieces, character sealbooks, a party built for this fight) is not modelled. The fight is optional (the three supply devices weaken the Queen, N04, met). Closed as a known limit, confirmed by the user on 2026-10-09</t>
+          <t>Not met by the model: 0 - 17% at level 55 whatever the share of forged enchantments, and 0 - 7.5% with the best meal of the ice cream and ramen shops in the best case (its buffs at the start of the fight, 40 battles, 2026-10-09). What a player at 55 adds beyond the model (unique pieces, character sealbooks, a party built for this fight) is not modelled. The fight is optional (the three supply devices weaken the Queen, N04, met). Closed as a known limit, confirmed on 2026-10-09</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>It adds the stats of the enemy of her sealbook to her dolls; the reference parties carry no sealbook yet (BALANCE_PLAN, sealbooks stay in the model; theme T10). Until then the Soul Summoner is measured without it.</t>
+          <t>It adds the stats of the enemy of her sealbook to her dolls; the reference parties carry no sealbook yet (the project notes, sealbooks stay in the model; theme T10). Until then the Soul Summoner is measured without it.</t>
         </is>
       </c>
     </row>
@@ -14864,7 +14864,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>decided by the user (BALANCE_PLAN.md section 6, 2026-10-07); docs/generated/CHECKPOINT_LEVELS.md</t>
+          <t>decided (the project notes section 6, 2026-10-07); docs/generated/CHECKPOINT_LEVELS.md</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -15290,7 +15290,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>the user's decision of 2026-10-08 (option 1: the reference party wears prepared, enchanted gear)</t>
+          <t>the decision of 2026-10-08 (option 1: the reference party wears prepared, enchanted gear)</t>
         </is>
       </c>
     </row>
@@ -15322,7 +15322,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>the code as read (the binary comes before the guides; the user left it to judgement on 2026-10-08). The wiki test is kept as a known discrepancy: chants with chant speed UP may be up to a tenth slower in the model than that test measured</t>
+          <t>the code as read (the binary comes before the guides; left to judgement on 2026-10-08). The wiki test is kept as a known discrepancy: chants with chant speed UP may be up to a tenth slower in the model than that test measured</t>
         </is>
       </c>
     </row>
@@ -15354,7 +15354,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>a choice the user took on 2026-10-08 (model enchanted gear)</t>
+          <t>a choice taken on 2026-10-08 (model enchanted gear)</t>
         </is>
       </c>
     </row>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>the user, 2026-10-09: each class measured at the stage where it is played, against several bosses of it; the class path changes at 15 and 30 (scenario.class_path)</t>
+          <t>decided 2026-10-09: each class measured at the stage where it is played, against several bosses of it; the class path changes at 15 and 30 (scenario.class_path)</t>
         </is>
       </c>
     </row>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>the user, 2026-10-09: each class measured at the stage where it is played, against several bosses of it; the class path changes at 15 and 30 (scenario.class_path)</t>
+          <t>decided 2026-10-09: each class measured at the stage where it is played, against several bosses of it; the class path changes at 15 and 30 (scenario.class_path)</t>
         </is>
       </c>
     </row>
@@ -15488,7 +15488,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>the user, 2026-10-09: each class measured at the stage where it is played, against several bosses of it; the class path changes at 15 and 30 (scenario.class_path) | C30 in the place of C29 since 2026-10-11: the model does not play Calliope as the guide describes (docs/generated/GUIDE_CURVE.md, policy gap; Settings boss_fit_skip), and that one fight set the verdict of six roles</t>
+          <t>decided 2026-10-09: each class measured at the stage where it is played, against several bosses of it; the class path changes at 15 and 30 (scenario.class_path) | C30 in the place of C29 since 2026-10-11: the model does not play Calliope as the guide describes (docs/generated/GUIDE_CURVE.md, policy gap; Settings boss_fit_skip), and that one fight set the verdict of six roles</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>the user, 2026-10-09: only the postgame bosses the model reproduces (within the floor of the GameFAQs class with margin, docs/generated/GUIDE_CURVE.md); the rest of the postgame is a known limit until theme T08</t>
+          <t>decided 2026-10-09: only the postgame bosses the model reproduces (within the floor of the GameFAQs class with margin, docs/generated/GUIDE_CURVE.md); the rest of the postgame is a known limit until theme T08</t>
         </is>
       </c>
     </row>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>The same party with a Diva in its last place (commit d25c8ed, 2026-10-11): the archetype with a healer and TP support. It takes the place of the party without a Diva (the user, 2026-10-11): that one ignores the basics, and whoever plays it can swap one member</t>
+          <t>The same party with a Diva in its last place (commit d25c8ed, 2026-10-11): the archetype with a healer and TP support. It takes the place of the party without a Diva (decided 2026-10-11): that one ignores the basics, and whoever plays it can swap one member</t>
         </is>
       </c>
     </row>
@@ -17275,7 +17275,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>The same party with a Diva in its last place (commit d25c8ed, 2026-10-11): the archetype with a healer and TP support. It takes the place of the party without a Diva (the user, 2026-10-11): that one ignores the basics, and whoever plays it can swap one member</t>
+          <t>The same party with a Diva in its last place (commit d25c8ed, 2026-10-11): the archetype with a healer and TP support. It takes the place of the party without a Diva (decided 2026-10-11): that one ignores the basics, and whoever plays it can swap one member</t>
         </is>
       </c>
     </row>
@@ -17797,7 +17797,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>model choice 2026-10-09: the user asked to use the difficulty the guide gives each boss as a point of comparison</t>
+          <t>model choice 2026-10-09: it was asked to use the difficulty the guide gives each boss as a point of comparison</t>
         </is>
       </c>
     </row>
@@ -17817,7 +17817,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>model choice 2026-10-09: the user asked to use the difficulty the guide gives each boss as a point of comparison</t>
+          <t>model choice 2026-10-09: it was asked to use the difficulty the guide gives each boss as a point of comparison</t>
         </is>
       </c>
     </row>
@@ -17837,7 +17837,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>model choice 2026-10-09: the user asked to use the difficulty the guide gives each boss as a point of comparison</t>
+          <t>model choice 2026-10-09: it was asked to use the difficulty the guide gives each boss as a point of comparison</t>
         </is>
       </c>
     </row>
@@ -17937,7 +17937,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>model choice 2026-10-09: the user asked for faster runs</t>
+          <t>model choice 2026-10-09: it was asked for faster runs</t>
         </is>
       </c>
     </row>
@@ -17957,7 +17957,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>model choice 2026-10-09: the user asked for faster runs</t>
+          <t>model choice 2026-10-09: it was asked for faster runs</t>
         </is>
       </c>
     </row>
@@ -18185,7 +18185,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>the user, 2026-10-11</t>
+          <t>decided 2026-10-11</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -17637,7 +17637,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>choice: about two standard errors of 40 battles near a share of 0.7</t>
+          <t>choice: about one standard error of the difference of two shares of 40 battles near 0.7 (each share is known to about 7 points), so a crossing by less than 15 points may be chance: measures/curve_recheck.py settles it with 200 battles</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -18242,7 +18242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19686,7 +19686,7 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -19700,7 +19700,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 138: the Sage raises the abilities of the party (Circle Brave kept up) | last since 2026-10-11: the attack buff serves the fewest members of the parties a Sage is in</t>
+          <t>atwiki dt2-2 page 138: the Sage raises the abilities of the party (Circle Brave kept up) | last since 2026-10-11: the attack buff serves the fewest members of the parties a Sage is in | 2026-10-13 : second, after Circle Protect: at the end of the list she never came to cast it. Sun Veil, Amplify and Accelerator left her rules the same day: each added nothing that could be measured at C30, C36, C38, C40 and P24 (150 battles, with and without each), and with the five kept up she never attacked. With the two buffs and then her spells she wins 90% of those fights in the last place of the reference party, against 87%</t>
         </is>
       </c>
     </row>
@@ -19736,7 +19736,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -19745,23 +19745,23 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>status:163</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sun Veil kept up</t>
+          <t>the mean damage per time of every skill</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>sage</t>
+          <t>shooter</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -19770,48 +19770,48 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>status:172</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Amplify kept up</t>
+          <t>the mean damage per time of every skill</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>sage</t>
+          <t>soul summoner</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>doll_slot_free</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>status:168</t>
+          <t>doll:Mercidarian|Spartan|Musiy|Catalina|Oracles</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Accelerator (one ally, 3 turns) after the party-wide buffs</t>
+          <t>atwiki dt2-2 pages 131, 146: both doll slots kept filled; GameFAQs Class Skill info - Spieler: Mercidarian by far the best doll</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>sage</t>
+          <t>soul summoner</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>shooter</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -19840,67 +19840,67 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>ally_down</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>the mean damage per time of every skill</t>
+          <t>GameFAQs faqs/80834 (balance_criteria F01): a party holds a Maid, a dispeller and a healer</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>soul summoner</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>doll_slot_free</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>doll:Mercidarian|Spartan|Musiy|Catalina|Oracles</t>
+          <t>status:170</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 pages 131, 146: both doll slots kept filled; GameFAQs Class Skill info - Spieler: Mercidarian by far the best doll</t>
+          <t>atwiki dt2-2 page 133: the Valkyrie draws attacks as the wall of the party</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>soul summoner</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>party_hp_below:0.5</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>heal:0.5</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>the mean damage per time of every skill</t>
+          <t>atwiki dt2-2 page 133</t>
         </is>
       </c>
     </row>
@@ -19911,21 +19911,21 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ally_down</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>status:162</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834 (balance_criteria F01): a party holds a Maid, a dispeller and a healer</t>
+          <t>atwiki dt2-2 page 122: the Paladin uses herself as the shield of the party (Protect kept up on the weakest member)</t>
         </is>
       </c>
     </row>
@@ -19936,7 +19936,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -19945,87 +19945,87 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>status:170</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 133: the Valkyrie draws attacks as the wall of the party</t>
+          <t>the mean damage per time of every skill</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>treasure hunter</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>party_hp_below:0.5</t>
+          <t>ally_down</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>heal:0.5</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 133</t>
+          <t>GameFAQs faqs/80834, Recommended Party: "can help with items in emergency situations"</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>treasure hunter</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>ally_tp_below:0.15</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>status:162</t>
+          <t>tp:0.15</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 122: the Paladin uses herself as the shield of the party (Protect kept up on the weakest member)</t>
+          <t>a fruit when a member runs dry (the items of the sheet Kit)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>treasure hunter</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>ally_hp_below:0.35</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>heal:0.35</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>the mean damage per time of every skill</t>
+          <t>GameFAQs faqs/80834, Recommended Party: items in an emergency</t>
         </is>
       </c>
     </row>
@@ -20036,96 +20036,96 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ally_down</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: "can help with items in emergency situations"</t>
+          <t>GameFAQs faqs/80834, Recommended Party: Pursuit Stab as the core</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>treasure hunter</t>
+          <t>valkyrie</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ally_tp_below:0.15</t>
+          <t>ally_down</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>tp:0.15</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>a fruit when a member runs dry (the items of the sheet Kit)</t>
+          <t>items when a member falls</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>treasure hunter</t>
+          <t>valkyrie</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ally_hp_below:0.35</t>
+          <t>ally_tp_below:0.15</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>heal:0.35</t>
+          <t>tp:0.15</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: items in an emergency</t>
+          <t>a fruit when a member runs dry (the items of the sheet Kit)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>treasure hunter</t>
+          <t>valkyrie</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>party_hp_below:0.5</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>heal:0.5</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: Pursuit Stab as the core</t>
+          <t>GameFAQs faqs/80834, Recommended Party: "in serious bosses she should usually be supporting"</t>
         </is>
       </c>
     </row>
@@ -20136,21 +20136,21 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>ally_down</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>status:183</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>items when a member falls</t>
+          <t>GameFAQs faqs/80834, Recommended Party: the guard buffs of the party</t>
         </is>
       </c>
     </row>
@@ -20161,21 +20161,21 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ally_tp_below:0.15</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>tp:0.15</t>
+          <t>status:161</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>a fruit when a member runs dry (the items of the sheet Kit)</t>
+          <t>GameFAQs faqs/80834, Recommended Party: War Cry maxed early</t>
         </is>
       </c>
     </row>
@@ -20186,21 +20186,21 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>party_hp_below:0.5</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>heal:0.5</t>
+          <t>status:180</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: "in serious bosses she should usually be supporting"</t>
+          <t>GameFAQs faqs/80834, Recommended Party: the Valkyrie prebuffs Parry and Cover in hard fights</t>
         </is>
       </c>
     </row>
@@ -20211,21 +20211,21 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>status:183</t>
+          <t>status:171</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: the guard buffs of the party</t>
+          <t>GameFAQs faqs/80834, Recommended Party: the Valkyrie prebuffs Parry and Cover in hard fights</t>
         </is>
       </c>
     </row>
@@ -20236,7 +20236,7 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -20245,98 +20245,98 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>status:161</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: War Cry maxed early</t>
+          <t>GameFAQs faqs/80834, Recommended Party: Daedalus, "one of the best fire and forget nukes"</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>valkyrie</t>
+          <t>mage</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>6</v>
+        <v>0.5</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>ally_tp_below:0.15</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>status:180</t>
+          <t>tp:0.15</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: the Valkyrie prebuffs Parry and Cover in hard fights</t>
+          <t>a fruit when a member runs dry (the items of the sheet Kit), as the roles of the reference party do: without it these roles left the eight Fairy Apples of the bag unused and fought on with plain attacks (diagnosis of C32, C36 and C40, 2026-10-11)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>valkyrie</t>
+          <t>sage</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>7</v>
+        <v>2.5</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>ally_tp_below:0.15</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>status:171</t>
+          <t>tp:0.15</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: the Valkyrie prebuffs Parry and Cover in hard fights</t>
+          <t>a fruit when a member runs dry (the items of the sheet Kit), as the roles of the reference party do: without it these roles left the eight Fairy Apples of the bag unused and fought on with plain attacks (diagnosis of C32, C36 and C40, 2026-10-11)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>valkyrie</t>
+          <t>healer</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>ally_tp_below:0.15</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>tp:0.15</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: Daedalus, "one of the best fire and forget nukes"</t>
+          <t>a fruit when a member runs dry (the items of the sheet Kit), as the roles of the reference party do: without it these roles left the eight Fairy Apples of the bag unused and fought on with plain attacks (diagnosis of C32, C36 and C40, 2026-10-11)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>mage</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -20357,11 +20357,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>sage</t>
+          <t>magical princess</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -20382,11 +20382,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>healer</t>
+          <t>mistress</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -20407,11 +20407,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>soul summoner</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>magical princess</t>
+          <t>dolls</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -20457,7 +20457,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>mistress</t>
+          <t>attacker</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -20482,7 +20482,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>soul summoner</t>
+          <t>kunoichi</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -20507,7 +20507,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>dolls</t>
+          <t>shooter</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -20532,7 +20532,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>attacker</t>
+          <t>joker</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -20549,81 +20549,6 @@
         </is>
       </c>
       <c r="E92" t="inlineStr">
-        <is>
-          <t>a fruit when a member runs dry (the items of the sheet Kit), as the roles of the reference party do: without it these roles left the eight Fairy Apples of the bag unused and fought on with plain attacks (diagnosis of C32, C36 and C40, 2026-10-11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>kunoichi</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>ally_tp_below:0.15</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>tp:0.15</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>a fruit when a member runs dry (the items of the sheet Kit), as the roles of the reference party do: without it these roles left the eight Fairy Apples of the bag unused and fought on with plain attacks (diagnosis of C32, C36 and C40, 2026-10-11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>shooter</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>ally_tp_below:0.15</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>tp:0.15</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>a fruit when a member runs dry (the items of the sheet Kit), as the roles of the reference party do: without it these roles left the eight Fairy Apples of the bag unused and fought on with plain attacks (diagnosis of C32, C36 and C40, 2026-10-11)</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>joker</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>ally_tp_below:0.15</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>tp:0.15</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
         <is>
           <t>a fruit when a member runs dry (the items of the sheet Kit), as the roles of the reference party do: without it these roles left the eight Fairy Apples of the bag unused and fought on with plain attacks (diagnosis of C32, C36 and C40, 2026-10-11)</t>
         </is>
@@ -21687,7 +21612,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Heal; Circle Brave; Circle Protect; Accelerator; Amplify; Sun Veil; Dispel; Esarhaddon; Slow; Stab Guard; Slash Guard; Bash Guard; Prism Dawn; Fast Cast; Sleep; Silence</t>
+          <t>Heal; Circle Brave; Circle Protect; Fireball; Ice Edge; Thunderbolt; Air Cutter; Stone Hammer; Accelerator; Amplify; Sun Veil; Dispel; Esarhaddon; Slow; Stab Guard; Slash Guard; Bash Guard; Prism Dawn; Fast Cast; Sleep; Silence; Bible Thump</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -21697,7 +21622,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 138 (support: party buffs, ailments, automatic cure); GameFAQs faqs/80834 (Hentaicheg), Class Skill info pages</t>
+          <t>atwiki dt2-2 page 138 (support: party buffs, ailments, automatic cure); GameFAQs faqs/80834 (Hentaicheg), Class Skill info pages | 2026-10-13 : she holds the five spells of the Magic User she was and Bible Thump (the classes of her path learn them); without them she dealt none of the damage of the party</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -17290,7 +17290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D46"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18228,6 +18228,46 @@
       <c r="D46" t="inlineStr">
         <is>
           <t>docs/generated/GUIDE_CURVE.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>heal_reserve_casts</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TP a member whose rules heal keeps back from her buffs and attacks: this many casts of her cheapest heal (sim/policy.py heal_reserve)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>choice (2026-10-13): what a player who is the heal of a party does; without it the Sage of the party Mage-Heavy spent the TP of the party on Fireball and on casting her buffs again</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>party_buff_recast_share</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>A buff of the whole party is cast again when at least this share of its members lack it</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>choice (2026-10-13): one member who lost it alone does not call for 22 TP</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -17290,7 +17290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18268,6 +18268,26 @@
       <c r="D48" t="inlineStr">
         <is>
           <t>choice (2026-10-13): one member who lost it alone does not call for 22 TP</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>punished_blow_floor</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>A plain blow that takes less than this share of the max HP of an enemy with Avenger or Dark Aura is not struck: the member defends (sim/policy.py weak_blow)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>choice (2026-10-13): a blow worth less than a hundredth of the boss is not worth a tenth of every stat</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -9892,7 +9892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11558,6 +11558,40 @@
       <c r="C98" t="inlineStr">
         <is>
           <t>The party of the sheets wins 0% at level 99 (floor of a hard boss 20%): it wears the gear of the guide and none of the answers a player prepares for the fight. Even with a crown bonus of 50 it wins 0%: the fight asks for an answer the policy does not play (sheet PostgameBosses, what the pages say). Measured on 2026-10-12 on the bosses below their floor (postgame_levers.py): a crown bonus of 50 alone brings 18 of 28 above it; max HP x1.5 with three pieces of "received damage DOWN" 11 of 28; the order of the Valkyrie's Cover and Parry changes nothing</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>34 Cleanse</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>A cure aimed at one ally: the prepared battle aims it at a member with no ailment. Aimed at the member poisoned and asleep it removes both (probe_two_actives_2026-10-15.py, recheck 2026-10-15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>142 Heaven or Hell Effect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>The heal of a random move, aimed at a foe: the prepared foes are at full HP. A foe at half HP regains 10% of its max HP, under the cap of 555 (probe_two_actives_2026-10-15.py, recheck 2026-10-15).</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -10673,14 +10673,14 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Her two dance slots hold Fascinating Waltz and Dumbing Mazurka (rules status:195, 201).</t>
+          <t>Her two dance slots hold Fascinating Waltz and Debilitating Salsa (rules status:195, 199).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>usage etoile | Debilitating Salsa</t>
+          <t>usage etoile | Dumbing Mazurka</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -10690,7 +10690,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Her two dance slots hold Fascinating Waltz and Dumbing Mazurka.</t>
+          <t>Her two dance slots hold Fascinating Waltz and Debilitating Salsa (rules status:195, 199). Waltz and Salsa win as often as Waltz and Mazurka and end the fights 5 - 33% sooner at C22 - C40 and P24 (measures/etoile_dances.py, 2026-10-15).</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Her two dance slots hold Fascinating Waltz and Dumbing Mazurka.</t>
+          <t>Her two dance slots hold Fascinating Waltz and Debilitating Salsa (rules status:195, 199).</t>
         </is>
       </c>
     </row>
@@ -10724,7 +10724,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Her two dance slots hold Fascinating Waltz and Dumbing Mazurka.</t>
+          <t>Her two dance slots hold Fascinating Waltz and Debilitating Salsa (rules status:195, 199).</t>
         </is>
       </c>
     </row>
@@ -10741,7 +10741,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Her two dance slots hold Fascinating Waltz and Dumbing Mazurka.</t>
+          <t>Her two dance slots hold Fascinating Waltz and Debilitating Salsa (rules status:195, 199).</t>
         </is>
       </c>
     </row>
@@ -18889,12 +18889,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>status:201</t>
+          <t>status:199</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dumbing Mazurka on the enemies</t>
+          <t>Debilitating Salsa on the enemies</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -9892,7 +9892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11592,6 +11592,142 @@
       <c r="C100" t="inlineStr">
         <is>
           <t>The heal of a random move, aimed at a foe: the prepared foes are at full HP. A foe at half HP regains 10% of its max HP, under the cap of 555 (probe_two_actives_2026-10-15.py, recheck 2026-10-15).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>276 Absolute Attack</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Effect 307 cancels the answers of the target to a blow (Avenger 249, Counter Whip 303, effect 250, the unique skill 447). Samael (C38) has none of them, so nothing changes there.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>302 Barrage</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Effect 251 adds two hits to a plain attack only. At C38 the skills of the Kunoichi always score above her plain attack, so she never makes one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>usage soul summoner | Spartan</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>doll order</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Her rule fills both doll slots in the order Mercidarian, Spartan, Musiy, Catalina, Oracles: Mercidarian takes both slots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>usage sage | Accelerator</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>role choice</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Left out of her rules on 2026-10-13 (sheet Policies, rule status:161): each added nothing that could be measured at C30, C36, C38, C40 and P24 (150 battles, with and without each), and with all five kept up she never attacked. She keeps Circle Protect and Circle Brave, then casts her spells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>usage sage | Amplify</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>role choice</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Left out of her rules on 2026-10-13 (sheet Policies, rule status:161): each added nothing that could be measured at C30, C36, C38, C40 and P24 (150 battles, with and without each), and with all five kept up she never attacked. She keeps Circle Protect and Circle Brave, then casts her spells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>usage sage | Sun Veil</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>role choice</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Left out of her rules on 2026-10-13 (sheet Policies, rule status:161): each added nothing that could be measured at C30, C36, C38, C40 and P24 (150 battles, with and without each), and with all five kept up she never attacked. She keeps Circle Protect and Circle Brave, then casts her spells.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>usage sage | Bible Thump</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>role choice</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>A tome skill: the Sage of the model holds no tome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>usage kunoichi | Phoenix</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>role choice</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>A projectile skill: the Kunoichi of the model holds a Tantou.</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -9581,7 +9581,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>test_sim_formulas.TurnOrder</t>
+          <t>engine_cs CalibrationTests.K01_TurnOrderReproducesTheSpeedTestOfTheJapaneseWiki</t>
         </is>
       </c>
     </row>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>test_sim_calibration.ChantSpeed</t>
+          <t>engine_cs CalibrationTests.K02_EachPieceShortensTheChantUntilTheThird</t>
         </is>
       </c>
     </row>
@@ -9655,7 +9655,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>test_sim_calibration.CriticalFactor</t>
+          <t>engine_cs CalibrationTests.K03_TheSealbookTestFitsAQuarterMore</t>
         </is>
       </c>
     </row>
@@ -9692,7 +9692,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>test_sim_calibration.DaedalusAttack</t>
+          <t>engine_cs CalibrationTests.K04_EveryMeasuredDaedalusAttackFallsInTheRangeOfTheFormula</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>test_sim_calibration.SummonStats</t>
+          <t>engine_cs CalibrationTests.K05_SummonStatsAreTheBestOfThePartyTimesTheFactorOfTheForm</t>
         </is>
       </c>
     </row>
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>test_sim_calibration.ChantStat</t>
+          <t>test_calibration.ChantStat</t>
         </is>
       </c>
     </row>
@@ -9803,7 +9803,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>test_sim_calibration.EncounterSteps</t>
+          <t>test_calibration.EncounterSteps</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>test_sim_calibration.GenerousHeart</t>
+          <t>test_calibration.GenerousHeart; engine_cs CalibrationTests.K08_MaidMasteryTakesGenerousHeartTo22Percent</t>
         </is>
       </c>
     </row>
@@ -9877,7 +9877,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>tools/sim_anchors.py N05, N06</t>
+          <t>dtcli sim-anchors N05, N06</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -18691,7 +18691,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: "the rotation is Power Charge &gt; Nuke"</t>
+          <t>Berserk kept up before Power Charge, so that the turn after the charge is a blow (2026-10-16: with the charge first, the charged turn went to Berserk; dtcli trace C29 Meta)</t>
         </is>
       </c>
     </row>
@@ -18716,7 +18716,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -21713,7 +21713,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Spartan; Catalina; Doll Mastery; Double Puppet; Mercidarian; Perdurabo; Musiy; Oracles; Destiny Line; Coffee Break; Weapon Mastery; Danger Shoot</t>
+          <t>Spartan; Catalina; Doll Mastery; Double Puppet; Mercidarian; Perdurabo; Musiy; Soul Eater; Oracles; Destiny Line; Coffee Break; Weapon Mastery; Danger Shoot</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -21190,7 +21190,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Fireball; Magic Mastery; Concentrate; Economy; Critical Magic; Thunderbolt; Fast Cast; Ice Edge; Crimson Flare; Muon Plasma; Cocytus; Tempest; Gaia Crush; Fire Blast; Ice Storm; Inferno; Diamond Dust; Meteor; Nirvana</t>
+          <t>Fireball; Crimson Flare; Magic Mastery; Concentrate; Inferno; Economy; Critical Magic; Thunderbolt; Fast Cast; Ice Edge; Muon Plasma; Cocytus; Tempest; Gaia Crush; Fire Blast; Ice Storm; Diamond Dust; Meteor; Nirvana</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -18472,7 +18472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834 (balance_criteria F01): a party holds a Maid, a dispeller and a healer</t>
+          <t>GameFAQs faqs/80834, Recommended Party: items when a member falls | 2026-10-16: the maid role plays by the rows of the diva role (her path ends in the Diva; class-stages C40 28% with her own rows)</t>
         </is>
       </c>
     </row>
@@ -19545,17 +19545,17 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ally_hp_below:0.5</t>
+          <t>ally_hp_below:0.35</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>heal:0.5</t>
+          <t>heal:0.35</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 120: the Maid restores HP and TP at no cost</t>
+          <t>GameFAQs faqs/80834, Recommended Party: First Aid or an item in an emergency | 2026-10-16: the maid role plays by the rows of the diva role (her path ends in the Diva; class-stages C40 28% with her own rows)</t>
         </is>
       </c>
     </row>
@@ -19570,17 +19570,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ally_tp_below:0.4</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>tp:0.4</t>
+          <t>status:215</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 120</t>
+          <t>GameFAQs faqs/80834, Recommended Party: "upkeeps Heal/Speed song in boss battles"; the heal song first | 2026-10-16: the maid role plays by the rows of the diva role (her path ends in the Diva; class-stages C40 28% with her own rows)</t>
         </is>
       </c>
     </row>
@@ -19600,12 +19600,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>status:215</t>
+          <t>status:217</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 129: Replenishing Carol</t>
+          <t>GameFAQs faqs/80834, Recommended Party: the speed song | 2026-10-16: the maid role plays by the rows of the diva role (her path ends in the Diva; class-stages C40 28% with her own rows)</t>
         </is>
       </c>
     </row>
@@ -19620,42 +19620,42 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>ally_tp_below:0.35</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>tp:0.35</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>the mean damage per time of every skill</t>
+          <t>GameFAQs faqs/80834, Recommended Party: "helps manage the party TP with cook and self sacrifice" | 2026-10-16: the maid role plays by the rows of the diva role (her path ends in the Diva; class-stages C40 28% with her own rows)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>mistress</t>
+          <t>maid</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ally_down</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Resurrect or items</t>
+          <t>the mean damage per time of every skill | 2026-10-16: the maid role plays by the rows of the diva role (her path ends in the Diva; class-stages C40 28% with her own rows)</t>
         </is>
       </c>
     </row>
@@ -19666,21 +19666,21 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>ally_down</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>status:215</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>the heal song kept up</t>
+          <t>Resurrect or items</t>
         </is>
       </c>
     </row>
@@ -19691,7 +19691,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -19700,12 +19700,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>status:161</t>
+          <t>status:215</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>War Cry kept up</t>
+          <t>the heal song kept up</t>
         </is>
       </c>
     </row>
@@ -19716,7 +19716,7 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -19725,37 +19725,37 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>status:161</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>the mean damage per time of every skill</t>
+          <t>War Cry kept up</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>papillon</t>
+          <t>mistress</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ally_down</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>items when a member falls</t>
+          <t>the mean damage per time of every skill</t>
         </is>
       </c>
     </row>
@@ -19766,21 +19766,21 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ally_tp_below:0.15</t>
+          <t>ally_down</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>tp:0.15</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>a fruit when a member runs dry (the items of the sheet Kit)</t>
+          <t>items when a member falls</t>
         </is>
       </c>
     </row>
@@ -19791,46 +19791,46 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>ally_tp_below:0.15</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>tp:0.15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: the best area attack and the damage of the party</t>
+          <t>a fruit when a member runs dry (the items of the sheet Kit)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>sage</t>
+          <t>papillon</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ally_down</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>items when a member falls</t>
+          <t>GameFAQs faqs/80834, Recommended Party: the best area attack and the damage of the party</t>
         </is>
       </c>
     </row>
@@ -19841,21 +19841,21 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>party_hp_below:0.5</t>
+          <t>ally_down</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>heal:0.5</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>heals when the party is low</t>
+          <t>items when a member falls</t>
         </is>
       </c>
     </row>
@@ -19866,21 +19866,21 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>enemy_buffed</t>
+          <t>party_hp_below:0.5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>dispel</t>
+          <t>heal:0.5</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dispel against boss buffs</t>
+          <t>heals when the party is low</t>
         </is>
       </c>
     </row>
@@ -19891,21 +19891,21 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>enemy_buffed</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ailment:122;117;116</t>
+          <t>dispel</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 138: the Sage supports with ailment spells; slow, silence and sleep in that order (page 227 names slow and silence against the heal wall of Calliope)</t>
+          <t>Dispel against boss buffs</t>
         </is>
       </c>
     </row>
@@ -19916,21 +19916,21 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>status:161</t>
+          <t>ailment:122;117;116</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 138: the Sage raises the abilities of the party (Circle Brave kept up) | last since 2026-10-11: the attack buff serves the fewest members of the parties a Sage is in | 2026-10-13 : second, after Circle Protect: at the end of the list she never came to cast it. Sun Veil, Amplify and Accelerator left her rules the same day: each added nothing that could be measured at C30, C36, C38, C40 and P24 (150 battles, with and without each), and with the five kept up she never attacked. With the two buffs and then her spells she wins 90% of those fights in the last place of the reference party, against 87%</t>
+          <t>atwiki dt2-2 page 138: the Sage supports with ailment spells; slow, silence and sleep in that order (page 227 names slow and silence against the heal wall of Calliope)</t>
         </is>
       </c>
     </row>
@@ -19941,7 +19941,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -19950,12 +19950,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>status:162</t>
+          <t>status:161</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 138 (Circle Protect kept up)</t>
+          <t>atwiki dt2-2 page 138: the Sage raises the abilities of the party (Circle Brave kept up) | last since 2026-10-11: the attack buff serves the fewest members of the parties a Sage is in | 2026-10-13 : second, after Circle Protect: at the end of the list she never came to cast it. Sun Veil, Amplify and Accelerator left her rules the same day: each added nothing that could be measured at C30, C36, C38, C40 and P24 (150 battles, with and without each), and with the five kept up she never attacked. With the two buffs and then her spells she wins 90% of those fights in the last place of the reference party, against 87%</t>
         </is>
       </c>
     </row>
@@ -19966,7 +19966,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -19975,23 +19975,23 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>status:162</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>the mean damage per time of every skill</t>
+          <t>atwiki dt2-2 page 138 (Circle Protect kept up)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>shooter</t>
+          <t>sage</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>soul summoner</t>
+          <t>shooter</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -20020,17 +20020,17 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>doll_slot_free</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>doll:Mercidarian|Spartan|Musiy|Catalina|Oracles</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 pages 131, 146: both doll slots kept filled; GameFAQs Class Skill info - Spieler: Mercidarian by far the best doll</t>
+          <t>the mean damage per time of every skill</t>
         </is>
       </c>
     </row>
@@ -20041,46 +20041,46 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>doll_slot_free</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>doll:Mercidarian|Spartan|Musiy|Catalina|Oracles</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>the mean damage per time of every skill</t>
+          <t>atwiki dt2-2 pages 131, 146: both doll slots kept filled; GameFAQs Class Skill info - Spieler: Mercidarian by far the best doll</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>soul summoner</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ally_down</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834 (balance_criteria F01): a party holds a Maid, a dispeller and a healer</t>
+          <t>the mean damage per time of every skill</t>
         </is>
       </c>
     </row>
@@ -20091,21 +20091,21 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>ally_down</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>status:170</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 133: the Valkyrie draws attacks as the wall of the party</t>
+          <t>GameFAQs faqs/80834 (balance_criteria F01): a party holds a Maid, a dispeller and a healer</t>
         </is>
       </c>
     </row>
@@ -20116,21 +20116,21 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>party_hp_below:0.5</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>heal:0.5</t>
+          <t>status:170</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 133</t>
+          <t>atwiki dt2-2 page 133: the Valkyrie draws attacks as the wall of the party</t>
         </is>
       </c>
     </row>
@@ -20141,21 +20141,21 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>party_hp_below:0.5</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>status:162</t>
+          <t>heal:0.5</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 122: the Paladin uses herself as the shield of the party (Protect kept up on the weakest member)</t>
+          <t>atwiki dt2-2 page 133</t>
         </is>
       </c>
     </row>
@@ -20166,7 +20166,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -20175,37 +20175,37 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>status:162</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>the mean damage per time of every skill</t>
+          <t>atwiki dt2-2 page 122: the Paladin uses herself as the shield of the party (Protect kept up on the weakest member)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>treasure hunter</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ally_down</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: "can help with items in emergency situations"</t>
+          <t>the mean damage per time of every skill</t>
         </is>
       </c>
     </row>
@@ -20216,21 +20216,21 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ally_tp_below:0.15</t>
+          <t>ally_down</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tp:0.15</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>a fruit when a member runs dry (the items of the sheet Kit)</t>
+          <t>GameFAQs faqs/80834, Recommended Party: "can help with items in emergency situations"</t>
         </is>
       </c>
     </row>
@@ -20241,21 +20241,21 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ally_hp_below:0.35</t>
+          <t>ally_tp_below:0.15</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>heal:0.35</t>
+          <t>tp:0.15</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: items in an emergency</t>
+          <t>a fruit when a member runs dry (the items of the sheet Kit)</t>
         </is>
       </c>
     </row>
@@ -20266,46 +20266,46 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>ally_hp_below:0.35</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>heal:0.35</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: Pursuit Stab as the core</t>
+          <t>GameFAQs faqs/80834, Recommended Party: items in an emergency</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>valkyrie</t>
+          <t>treasure hunter</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ally_down</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>revive</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>items when a member falls</t>
+          <t>GameFAQs faqs/80834, Recommended Party: Pursuit Stab as the core</t>
         </is>
       </c>
     </row>
@@ -20316,21 +20316,21 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ally_tp_below:0.15</t>
+          <t>ally_down</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>tp:0.15</t>
+          <t>revive</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>a fruit when a member runs dry (the items of the sheet Kit)</t>
+          <t>items when a member falls</t>
         </is>
       </c>
     </row>
@@ -20341,21 +20341,21 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>party_hp_below:0.5</t>
+          <t>ally_tp_below:0.15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>heal:0.5</t>
+          <t>tp:0.15</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: "in serious bosses she should usually be supporting"</t>
+          <t>a fruit when a member runs dry (the items of the sheet Kit)</t>
         </is>
       </c>
     </row>
@@ -20366,21 +20366,21 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>party_hp_below:0.5</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>status:183</t>
+          <t>heal:0.5</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: the guard buffs of the party</t>
+          <t>GameFAQs faqs/80834, Recommended Party: "in serious bosses she should usually be supporting"</t>
         </is>
       </c>
     </row>
@@ -20391,7 +20391,7 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -20400,12 +20400,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>status:161</t>
+          <t>status:183</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: War Cry maxed early</t>
+          <t>GameFAQs faqs/80834, Recommended Party: the guard buffs of the party</t>
         </is>
       </c>
     </row>
@@ -20416,21 +20416,21 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>boss</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>status:180</t>
+          <t>status:161</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: the Valkyrie prebuffs Parry and Cover in hard fights</t>
+          <t>GameFAQs faqs/80834, Recommended Party: War Cry maxed early</t>
         </is>
       </c>
     </row>
@@ -20441,7 +20441,7 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -20450,7 +20450,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>status:171</t>
+          <t>status:180</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -20466,57 +20466,57 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>boss</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>damage</t>
+          <t>status:171</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834, Recommended Party: Daedalus, "one of the best fire and forget nukes"</t>
+          <t>GameFAQs faqs/80834, Recommended Party: the Valkyrie prebuffs Parry and Cover in hard fights</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>mage</t>
+          <t>valkyrie</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5</v>
+        <v>8</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ally_tp_below:0.15</t>
+          <t>always</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>tp:0.15</t>
+          <t>damage</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>a fruit when a member runs dry (the items of the sheet Kit), as the roles of the reference party do: without it these roles left the eight Fairy Apples of the bag unused and fought on with plain attacks (diagnosis of C32, C36 and C40, 2026-10-11)</t>
+          <t>GameFAQs faqs/80834, Recommended Party: Daedalus, "one of the best fire and forget nukes"</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>sage</t>
+          <t>mage</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -20537,7 +20537,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>healer</t>
+          <t>sage</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -20562,11 +20562,11 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>healer</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -20587,11 +20587,11 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>magical princess</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -20612,11 +20612,11 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>mistress</t>
+          <t>magical princess</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -20637,11 +20637,11 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>soul summoner</t>
+          <t>mistress</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -20662,7 +20662,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>dolls</t>
+          <t>soul summoner</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -20687,11 +20687,11 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>attacker</t>
+          <t>dolls</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -20712,11 +20712,11 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>kunoichi</t>
+          <t>attacker</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -20737,7 +20737,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>shooter</t>
+          <t>kunoichi</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -20762,23 +20762,48 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>shooter</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ally_tp_below:0.15</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>tp:0.15</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>a fruit when a member runs dry (the items of the sheet Kit), as the roles of the reference party do: without it these roles left the eight Fairy Apples of the bag unused and fought on with plain attacks (diagnosis of C32, C36 and C40, 2026-10-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>joker</t>
         </is>
       </c>
-      <c r="B92" t="n">
+      <c r="B93" t="n">
         <v>1.5</v>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C93" t="inlineStr">
         <is>
           <t>ally_tp_below:0.15</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="D93" t="inlineStr">
         <is>
           <t>tp:0.15</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>a fruit when a member runs dry (the items of the sheet Kit), as the roles of the reference party do: without it these roles left the eight Fairy Apples of the bag unused and fought on with plain attacks (diagnosis of C32, C36 and C40, 2026-10-11)</t>
         </is>
@@ -21041,7 +21066,11 @@
           <t>Megaphone</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Leather Shield</t>
+        </is>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Leather Helmet</t>
@@ -21074,7 +21103,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 pages 120, 129, 143</t>
+          <t>atwiki dt2-2 pages 120, 129, 143 | 2026-10-16: the skill plan and the Leather Shield of the diva role (GameFAQs faqs/80834, Hentaicheg), with the Maid skills of the start kept: with the priority list alone the Diva of this role won 28% at C40 (class-stages) against 71%.</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Replenishing Carol:max; Self Session:1; Song Mastery:max; First Aid:3; Cook:3; Generous Heart:3; Maid Mastery:3; Lightning March:3; Blissful Chorale:3; Maid Mastery:max; Generous Heart:max; Cook:max; First Aid:max; Lightning March:max; Concentration Prelude:max; Auto-Recovery:max; Fast Talk:max</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -21103,12 +21103,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 pages 120, 129, 143 | 2026-10-16: the skill plan and the Leather Shield of the diva role (GameFAQs faqs/80834, Hentaicheg), with the Maid skills of the start kept: with the priority list alone the Diva of this role won 28% at C40 (class-stages) against 71%.</t>
+          <t>atwiki dt2-2 pages 120, 129, 143 | 2026-10-16: the skill plan and the Leather Shield of the diva role (GameFAQs faqs/80834, Hentaicheg), with the Maid skills of the start kept: with the priority list alone the Diva of this role won 28% at C40 (class-stages) against 71%. | 2026-10-16: Cook:1 right after Self Session, so a plan never spends the points Cook needs (the TP of the party) on a level of Song Mastery.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Replenishing Carol:max; Self Session:1; Song Mastery:max; First Aid:3; Cook:3; Generous Heart:3; Maid Mastery:3; Lightning March:3; Blissful Chorale:3; Maid Mastery:max; Generous Heart:max; Cook:max; First Aid:max; Lightning March:max; Concentration Prelude:max; Auto-Recovery:max; Fast Talk:max</t>
+          <t>Replenishing Carol:max; Self Session:1; Cook:1; Song Mastery:max; First Aid:3; Cook:3; Generous Heart:3; Maid Mastery:3; Lightning March:3; Blissful Chorale:3; Maid Mastery:max; Generous Heart:max; Cook:max; First Aid:max; Lightning March:max; Concentration Prelude:max; Auto-Recovery:max; Fast Talk:max</t>
         </is>
       </c>
     </row>
@@ -21422,12 +21422,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834 (Hentaicheg), Recommended Party and Best in Slot Gear pages: Yuni Diva; the heal song maxed first, song mastery after, few points elsewhere, then the after-battle regeneration and maid mastery; Self Session level 1 as soon as possible (Class Skill info - Maid) so the heal and speed songs are kept up together, Lightning March kept up on bosses, Cook and Self-Sacrifice for TP</t>
+          <t>GameFAQs faqs/80834 (Hentaicheg), Recommended Party and Best in Slot Gear pages: Yuni Diva; the heal song maxed first, song mastery after, few points elsewhere, then the after-battle regeneration and maid mastery; Self Session level 1 as soon as possible (Class Skill info - Maid) so the heal and speed songs are kept up together, Lightning March kept up on bosses, Cook and Self-Sacrifice for TP | 2026-10-16: Cook:1 right after Self Session, so a plan never spends the points Cook needs (the TP of the party) on a level of Song Mastery.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Replenishing Carol:max; Self Session:1; Song Mastery:max; Lightning March:3; Cook:3; Self-Sacrifice:1; Generous Heart:3; Maid Mastery:3; Blissful Chorale:3; Lightning March:max; Generous Heart:max; Maid Mastery:max</t>
+          <t>Replenishing Carol:max; Self Session:1; Cook:1; Song Mastery:max; Lightning March:3; Cook:3; Self-Sacrifice:1; Generous Heart:3; Maid Mastery:3; Blissful Chorale:3; Lightning March:max; Generous Heart:max; Maid Mastery:max</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -9892,7 +9892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11728,6 +11728,23 @@
       <c r="C108" t="inlineStr">
         <is>
           <t>A projectile skill: the Kunoichi of the model holds a Tantou.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>299 Song Mastery</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>context</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>At C18 the songs of the maid role (a Bard, level 29) already keep the party at full HP and TP, so a larger song bonus changes no fight there. It serves where HP or TP run short: the skill battery reads it niche (best cell C38 boss, Mage-Heavy, fights 16% shorter; 2026-10-17). Unread since the maid role took the plan and policy of the diva (2026-10-16).</t>
         </is>
       </c>
     </row>
@@ -17460,7 +17477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -18458,6 +18475,26 @@
       <c r="D49" t="inlineStr">
         <is>
           <t>choice (2026-10-13): a blow worth less than a hundredth of the boss is not worth a tenth of every stat</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ailment_min_chance_123</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Shadow Sew (effect 123) is cast when its chance is at least this (the floor of ailment_min_chance for this effect alone): its roll is a fixed 30 - 40% by level, no resistance, and only on a target of a lower level than the user (docs/FORMULAS.md), so the general floor of 50% kept the model from ever casting it</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>model choice 2026-10-17 (audit M-02): the lowest chance of the skill, so it is cast where the program lets it land</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -32,6 +32,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueGear" sheetId="23" state="visible" r:id="rId23"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PersonalSealbooks" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BatteryParties" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MercenaryUnlocks" sheetId="26" state="visible" r:id="rId26"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17471,6 +17472,1032 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>From checkpoint</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Until checkpoint</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>135</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>story: chapter 7, the Tavern opens (temple of Wrappl)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>C26</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>story: chapter 7, after the event of the chapter</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>151</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>C27</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>story: chapter 8, its start</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>172</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C35</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>story: chapter 10, its start</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>197</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>story: chapter 11, its start</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>204</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>story: chapter 10 or 11 (the research gives both): taken at the start of chapter 11</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>211</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 51)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>215</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 52)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>220</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 54)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>224</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 57)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>230</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 55)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>250</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 82)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>263</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 62)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>284</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 64)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>318</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 78)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>319</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>C32</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>story: chapter 9, its start</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>320</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>C33</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>story: chapter 9, its progress</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>334</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>P24</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 89)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>353</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>C38</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>story: chapter 11, its progress: after the one checkpoint of the chapter (C37)</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>358</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>P28</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 91)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>359</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>P28</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 93)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>365</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>P33</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 99)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>370</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 60)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>374</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 84)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>376</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>P01</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 62)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>381</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 65)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>384</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>P02</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 65)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>385</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 67)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>386</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P33</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 99)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>388</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P28</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 93)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>400</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 69)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>402</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 68)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>407</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>P08</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 72)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>412</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>P28</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 93)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>418</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 78)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>928</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>P09</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 74)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>never: placeholder record 101</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>never: placeholder record 102</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>never: placeholder record 103</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>never: Michelle, a guest of the story, not hired at the Tavern</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>P24</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 85)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>P33</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 98)</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P33</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 97)</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P33</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 96)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P28</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 95)</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1089</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>C34</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>approximate: side event, where the flag is set is not mapped; open from the first checkpoint whose reference level reaches the stage (level 50)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1094</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>approximate: side event, where the flag is set is not mapped; open from the first checkpoint whose reference level reaches the stage (level 53)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1104</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>P24</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 86)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1106</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>C32</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>story: from the 9th talk event (chapter 8) to the 10th (chapter 9)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1419</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 82)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -17524,7 +17524,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17544,7 +17544,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17564,7 +17564,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17584,7 +17584,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17624,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17644,7 +17644,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17664,7 +17664,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17704,7 +17704,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17724,7 +17724,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17744,7 +17744,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17764,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17784,7 +17784,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17804,7 +17804,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17824,7 +17824,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17844,7 +17844,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17884,7 +17884,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17904,7 +17904,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17924,7 +17924,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17964,7 +17964,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -17984,7 +17984,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18004,7 +18004,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18024,7 +18024,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18044,7 +18044,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18064,7 +18064,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18084,7 +18084,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18124,7 +18124,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18144,7 +18144,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18164,7 +18164,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18184,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18204,7 +18204,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18224,7 +18224,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18254,7 +18254,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18284,7 +18284,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18304,7 +18304,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18324,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18344,7 +18344,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18364,7 +18364,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18404,7 +18404,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18424,7 +18424,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18444,7 +18444,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>
@@ -18489,7 +18489,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>measures/MERCENARY_RESEARCH.md 2.7 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -17519,12 +17519,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>story: chapter 7, the Tavern opens (temple of Wrappl)</t>
+          <t>story: evt02.pck/evt02.adv.bin (Main07_20_Start, chapter 7, the Tavern opens after C24)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17534,17 +17534,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>C26</t>
+          <t>C27</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>story: chapter 7, after the event of the chapter</t>
+          <t>story: evt02.pck/evt02.adv.bin (Main08_00_Start, start of chapter 8 after C26)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17554,17 +17554,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C27</t>
+          <t>C30</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>story: chapter 8, its start</t>
+          <t>story: St10_0010/Main08_09.adv.bin (Main08_15_Start, chapter 8 before C30)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17579,12 +17579,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>story: chapter 10, its start</t>
+          <t>story: evt02.pck/evt02.adv.bin (Main10_00_Start, start of chapter 10 after C34)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17594,17 +17594,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>C37</t>
+          <t>C36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>story: chapter 11, its start</t>
+          <t>story: St13_0140/Main10_25.adv.bin (Dreamscape 14F, after C35 on 14F, before C36 on 15F)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17619,12 +17619,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>story: chapter 10 or 11 (the research gives both): taken at the start of chapter 11</t>
+          <t>story: evt02.pck/evt02.adv.bin (Main11_00_Start, start of chapter 11 after C36)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17634,17 +17634,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 51)</t>
+          <t>story: St14_1040/Main11_07.adv.bin (Gruneworth 4F, chapter 11 before C37a)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17654,17 +17654,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 52)</t>
+          <t>story: St15_0010/Main12_00.adv.bin (Main12_00_Start, start of chapter 12 before C38)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17674,17 +17674,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 54)</t>
+          <t>story: St15_1060/Main12_05.adv.bin (after battle 41 Samael, C38)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17694,17 +17694,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>C39</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 57)</t>
+          <t>story: St15_1120/Main12_09.adv.bin (Main12_09_Start, before battle 41 Melek Taus, C39)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17719,12 +17719,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 55)</t>
+          <t>postgame: evt02.pck/evt02.adv.bin (Main20_00_Start, start of postgame after C40)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17734,17 +17734,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 82)</t>
+          <t>postgame: St00_1020/St00_c0020.adv.bin (after battle 41 Kuchinawa, P10)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17754,17 +17754,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 62)</t>
+          <t>postgame: St03_0011/St03_b0020.adv.bin (after battle 41 Kaguya on Vrachia North, before P05)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17774,17 +17774,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 64)</t>
+          <t>postgame: St06_0030/St06_c0050.adv.bin (after battle 44 Vitoria/Siegdrad/Airavata, P07)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17794,17 +17794,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P15</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 78)</t>
+          <t>postgame: St11_0010/St11_0090.adv.bin (after battle 45 Murasaki Shikibu, P14)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17814,17 +17814,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>C32</t>
+          <t>C33</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>story: chapter 9, its start</t>
+          <t>story: St12_0010/St12_a0110.adv.bin (after battle 41 Moby Dick, C32)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17834,17 +17834,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C33</t>
+          <t>C34</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>story: chapter 9, its progress</t>
+          <t>story: St12_0010/St12_a0130.adv.bin (after battle 42 Death Cataphract, C33)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17859,12 +17859,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 89)</t>
+          <t>postgame: St13_0030/St13_c0060.adv.bin (after battle 41 Samael Lv88, P23)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17879,12 +17879,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>story: chapter 11, its progress: after the one checkpoint of the chapter (C37)</t>
+          <t>story: St14_1010/St14_a0080.adv.bin (after battle 41 Iron Maiden, C37)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17894,17 +17894,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P25</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 91)</t>
+          <t>postgame: St14_1050/St14_e0060.adv.bin (after battle 42 7th Aradia, P24)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17919,12 +17919,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 93)</t>
+          <t>postgame: St14_1060/St14_f0040.adv.bin (after battle 41 Melek Taus Lv90, P27)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17939,12 +17939,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 99)</t>
+          <t>postgame: St15_1160/St15_q0030.adv.bin (after battle 41 8th Aradia, P32)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17954,17 +17954,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P03</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 60)</t>
+          <t>postgame: St20_1020/St20_c0040.adv.bin (after battle 42 Iktomi, P02)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17974,17 +17974,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 84)</t>
+          <t>postgame: St20_1040/St20_e0010.adv.bin (after battle 41 weakened Crom Cruach, P20)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -17994,17 +17994,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>P01</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 62)</t>
+          <t>postgame: St20_1040/St20_e0040.adv.bin (after battle 43 Sukuna-Hikona, P04)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18014,17 +18014,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 65)</t>
+          <t>postgame: St21_0010/St21_a0150.adv.bin (after battle 41 Jungfrau on Casino 1F, before P08)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18034,17 +18034,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 65)</t>
+          <t>postgame: St21_0020/St21_b0110.adv.bin (after battle 41 Qitian Dasheng, P08)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18054,17 +18054,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 67)</t>
+          <t>postgame: St21_0060/St21_f0020.adv.bin (after battle 41 Azathoth, P09)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18074,17 +18074,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P41</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 99)</t>
+          <t>postgame: St21_0060/St21_f0080.adv.bin (after battle 42 Casino VIP 7th fight, P40)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18094,17 +18094,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P31</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 93)</t>
+          <t>postgame: St21_0060/St21_f0100.adv.bin (after battle 45 weakened Lolo and Tenerezza, P30)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18114,17 +18114,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 69)</t>
+          <t>postgame: St22_1010/St22_a0110.adv.bin (after battle 41 Genbu, P12)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18134,17 +18134,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P12</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 68)</t>
+          <t>postgame: St22_1010/St22_a0020.adv.bin (Matrix 1F entry event, before P12)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18154,17 +18154,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P14</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 72)</t>
+          <t>postgame: St22_1020/St22_b0080.adv.bin (after battle 43 Nuwa, P13)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18174,17 +18174,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P32</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 93)</t>
+          <t>postgame: St22_1020/St22_b0540.adv.bin (after battle 45 weakened Magna Meretrix, P31)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18194,17 +18194,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P18</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 78)</t>
+          <t>postgame: St23_0060/St23_f0040.adv.bin (after battle 41 Last Judgment, P17)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18214,17 +18214,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 74)</t>
+          <t>postgame: evt02.pck/St93.adv.bin (after defeating Euthys on Vrachia North, P05)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18234,12 +18234,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>never: placeholder record 101</t>
+          <t>never: placeholder record 101 (Battle.pck/Main06_10.adv.bin, cleared in Item0885.pck/Main06_12.adv.bin)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18249,12 +18249,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>never: placeholder record 102</t>
+          <t>never: placeholder record 102 (Battle.pck/Main06_10.adv.bin, cleared in Item0885.pck/Main06_12.adv.bin)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18264,12 +18264,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>never: placeholder record 103</t>
+          <t>never: placeholder record 103 (St07_0010/Main06_13.adv.bin, cleared in Item0885.pck/Main06_12.adv.bin)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18279,12 +18279,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>never: Michelle, a guest of the story, not hired at the Tavern</t>
+          <t>never: Michelle, a guest of the story (joined by opcode 0x81, not hired at the Tavern)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18294,17 +18294,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P20</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 85)</t>
+          <t>postgame: SEV.pck/sev_296.adv.bin (after defeating Three Fates at Khorramshahr, P19)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18314,17 +18314,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P45</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 98)</t>
+          <t>postgame: St23_0040/St23_d0030.adv.bin (after battle 41 Yoshitsune, P44)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18334,17 +18334,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P43</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 97)</t>
+          <t>postgame: St21_1010/St21_g0020.adv.bin (after battle 41 Marduk, P42)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18354,17 +18354,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>P33</t>
+          <t>P42</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 96)</t>
+          <t>postgame: St20_1040/St20_e0140.adv.bin (after battle 45 Citlalinicue, P41)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18374,17 +18374,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>P28</t>
+          <t>P44</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 95)</t>
+          <t>postgame: St22_1020/St22_b0030.adv.bin (after battle 42 Arjuna, P43)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18394,17 +18394,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C34</t>
+          <t>C37</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>approximate: side event, where the flag is set is not mapped; open from the first checkpoint whose reference level reaches the stage (level 50)</t>
+          <t>side event: St10_0010/St10_0390.adv.bin (after battle 52 Azmaria Lv50 in Prizren Woods; party reaches Lv50 at C37)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18414,17 +18414,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C36</t>
+          <t>C38</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>approximate: side event, where the flag is set is not mapped; open from the first checkpoint whose reference level reaches the stage (level 53)</t>
+          <t>quest rank: QuestRankData_12.bin (Quest Rank 12, 390 pts; Miranda Lv53, party reaches Lv53 at C38)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18434,17 +18434,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>P24</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 86)</t>
+          <t>postgame: St21_1010/St21_g0010.adv.bin (Casino basement after Octopunch; Lv86, party reaches Lv86 at P21)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18464,12 +18464,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>story: from the 9th talk event (chapter 8) to the 10th (chapter 9)</t>
+          <t>story: St10_0010/cont_09.adv.bin (set in 9th talk event, chapter 8) to St12_0040/cont_10.adv.bin (cleared in 10th, chapter 9)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>
@@ -18479,17 +18479,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>P17</t>
+          <t>P21</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>approximate: postgame, where the flag is set is not mapped; open from the first postgame checkpoint whose reference level reaches the stage (level 82)</t>
+          <t>quest rank: 0x59618d SetFlag(quest_rank + 1400, 1) on QuestRankData_19.bin (Quest Rank 19, 840 pts; Lv82-90 stages)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>docs/FORMULAS.md 16.5 (the flag at 0xB4 of NPCData; the bar 0x58adb0); spoiler.jp dt2-2 傭兵バディ pages</t>
+          <t>docs/FORMULAS.md 16.5 (0x58adb0, 0x4c88ff, 0x59618d); Data/ENG/Script/*.pck, Dungeon.pck, QuestRankData.pck</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Every choice of the simulator of phase 1 (sim/) that is not a figure of the game: the policies of the party, the reference parties and their builds, the checkpoints, the settings of a run, the calibration tests and the assumptions the model still rests on. Figures of the game are read by sim/data.py from the game files; constants of the program stay in sim/formulas.py with their address.</t>
+          <t>Every choice of the battle model that is not a figure of the game: the policies of the party, the reference parties and their builds, the checkpoints, the settings of a run, the calibration tests and the assumptions the model still rests on. Figures of the game are read by gamedata/data.py from the game files; constants of the program stay in engine_cs/src/DtEngine/Formulas.cs with their address.</t>
         </is>
       </c>
     </row>
@@ -18826,7 +18826,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Battles played for each checkpoint a change touches, in vanilla and with the change (sim/measures.py check_change)</t>
+          <t>Battles played for each checkpoint a change touches, in vanilla and with the change (Measures.cs CheckChange)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Most random battles in a row an expedition measure plays (sim/measures.py expedition)</t>
+          <t>Most random battles in a row an expedition measure plays (Measures.cs Expedition)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>a role casts an ailment on an enemy only when its roll has at least this chance against the enemy's resistance (sim/policy.py act_ailment)</t>
+          <t>a role casts an ailment on an enemy only when its roll has at least this chance against the enemy's resistance (Policy.cs)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -19456,7 +19456,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TP a member whose rules heal keeps back from her buffs and attacks: this many casts of her cheapest heal (sim/policy.py heal_reserve)</t>
+          <t>TP a member whose rules heal keeps back from her buffs and attacks: this many casts of her cheapest heal (Policy.cs)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>A plain blow that takes less than this share of the max HP of an enemy with Avenger or Dark Aura is not struck: the member defends (sim/policy.py weak_blow)</t>
+          <t>A plain blow that takes less than this share of the max HP of an enemy with Avenger or Dark Aura is not struck: the member defends (Policy.cs)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -33,6 +33,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PersonalSealbooks" sheetId="24" state="visible" r:id="rId24"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BatteryParties" sheetId="25" state="visible" r:id="rId25"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MercenaryUnlocks" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CheckpointGuests" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18498,6 +18499,54 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Checkpoint</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Guest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Peggy &amp; Beard</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>atwiki dt2-2 page 227 (VS Calliope): the one boss Peggy &amp; Beard can be taken to; her Fireball from INT 500 deals 800 and more, enough to pass the heal wall of the Carol and the Splash</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -19478,14 +19478,10 @@
           <t>boss_fit_skip</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>C29</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Checkpoints tools/boss_fit.py gentle leaves alone: the model does not play them as the guide describes (docs/generated/GUIDE_CURVE.md, "read: policy gap")</t>
+          <t>Checkpoints tools/boss_fit.py gentle leaves alone: none since 2026-10-19 (C29 is played with the guide's preparation, sheet CheckpointGuests)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -9894,7 +9894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C109"/>
+  <dimension ref="A1:C115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11747,6 +11747,108 @@
       <c r="C109" t="inlineStr">
         <is>
           <t>At C18 the songs of the maid role (a Bard, level 29) already keep the party at full HP and TP, so a larger song bonus changes no fight there. It serves where HP or TP run short: the skill battery reads it niche (best cell C38 boss, Mage-Heavy, fights 16% shorter; 2026-10-17). Unread since the maid role took the plan and policy of the diva (2026-10-16).</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>curve P05</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>preparation gap</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>The party of the sheets wins 42% against Euthys on the engine corrected by the audit of 2026-10-18/19 (spells that miss deal half, the starting gauges and the AI as the program has them, the enchantments of the enemies counted): it wears the gear of the guide and none of the answers a player prepares for the fight. With a crown bonus of 40, the stand-in of the model for that preparation, it wins 100% (dtcli crown-trial, 200 battles, 2026-10-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>curve P25</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>preparation gap</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>The party of the sheets wins 68% against Mil the Overlord on the engine corrected by the audit of 2026-10-18/19 (spells that miss deal half, the starting gauges and the AI as the program has them, the enchantments of the enemies counted): it wears the gear of the guide and none of the answers a player prepares for the fight. With a crown bonus of 40, the stand-in of the model for that preparation, it wins 100% (dtcli crown-trial, 200 battles, 2026-10-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>curve P28</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>preparation gap</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>The party of the sheets wins 38% against Hell's Angel on the engine corrected by the audit of 2026-10-18/19 (spells that miss deal half, the starting gauges and the AI as the program has them, the enchantments of the enemies counted): it wears the gear of the guide and none of the answers a player prepares for the fight. With a crown bonus of 40, the stand-in of the model for that preparation, it wins 100% (dtcli crown-trial, 200 battles, 2026-10-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>curve P31</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>preparation gap</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>The party of the sheets wins 2% against the weakened Matrix superboss on the engine corrected by the audit of 2026-10-18/19 (spells that miss deal half, the starting gauges and the AI as the program has them, the enchantments of the enemies counted): it wears the gear of the guide and none of the answers a player prepares for the fight. With a crown bonus of 40, the stand-in of the model for that preparation, it wins 87% (dtcli crown-trial, 200 battles, 2026-10-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>curve P44</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>preparation gap</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>The party of the sheets wins 8% against Yoshitsune of the Wandering Brigade on the engine corrected by the audit of 2026-10-18/19 (spells that miss deal half, the starting gauges and the AI as the program has them, the enchantments of the enemies counted): it wears the gear of the guide and none of the answers a player prepares for the fight. With a crown bonus of 40, the stand-in of the model for that preparation, it wins 100% (dtcli crown-trial, 200 battles, 2026-10-19).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>curve P52</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>preparation gap</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>The party of the sheets wins 8% against Bearerophon on the engine corrected by the audit of 2026-10-18/19 (spells that miss deal half, the starting gauges and the AI as the program has them, the enchantments of the enemies counted): it wears the gear of the guide and none of the answers a player prepares for the fight. With a crown bonus of 40, the stand-in of the model for that preparation, it wins 98% (dtcli crown-trial, 200 battles, 2026-10-19).</t>
         </is>
       </c>
     </row>
@@ -19478,7 +19580,6 @@
           <t>boss_fit_skip</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
           <t>Checkpoints tools/boss_fit.py gentle leaves alone: none since 2026-10-19 (C29 is played with the guide's preparation, sheet CheckpointGuests)</t>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -19682,7 +19682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22016,6 +22016,56 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>a fruit when a member runs dry (the items of the sheet Kit), as the roles of the reference party do: without it these roles left the eight Fairy Apples of the bag unused and fought on with plain attacks (diagnosis of C32, C36 and C40, 2026-10-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ally_down</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>revive</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>items when a member falls, as the other roles of the support line do (2026-10-19: the role had no row for it)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>boss</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>status:187</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>the class kit: Divine Shield (skill 201) of the Priestess line, prebuffed in hard fights as the other support roles prebuff their guards (2026-10-19: the role never cast it; class-search showed her parties the lowest of the lowest HP from C27 on)</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -20530,7 +20530,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>always</t>
+          <t>no_foe_dispels</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -20540,7 +20540,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shadow Clone kept up (page 142)</t>
+          <t>Shadow Clone kept up (page 142) | 2026-10-19: not against foes whose attacks strip buffs (Death Cataphract, C33): she spent the fight casting it again after every plain blow and dealt almost no damage (class-search: a 50% stronger Ninja Piledriver left 76 of 83 Kunoichi parties of C33 unchanged)</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -16889,7 +16889,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17147,7 +17147,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>soul summoner</t>
+          <t>tank</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -17172,57 +17172,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>dolls</t>
+          <t>diva</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Persephone</t>
+          <t>Demi Lich</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834 (Hentaicheg), Best in Slot Gear + Sealbooks: Persephone (level 66, sealed in the first postgame dungeon), "can get it early and it is pretty solid forever" for physical roles</t>
+          <t>GameFAQs faqs/80834 (Hentaicheg), Best in Slot Gear + Sealbooks: Demi Lich (level 69), "a pretty early sealbook", for the Diva and offensive mages</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>tank</t>
+          <t>healer</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Persephone</t>
+          <t>Demi Lich</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834 (Hentaicheg), Best in Slot Gear + Sealbooks: Persephone (level 66, sealed in the first postgame dungeon), "can get it early and it is pretty solid forever" for physical roles</t>
+          <t>GameFAQs faqs/80834 (Hentaicheg), Best in Slot Gear + Sealbooks: Demi Lich (level 69), "a pretty early sealbook", for the Diva and offensive mages</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>diva</t>
+          <t>mage</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -17247,7 +17247,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>healer</t>
+          <t>sage</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -17272,7 +17272,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>mage</t>
+          <t>magical princess</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -17297,7 +17297,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sage</t>
+          <t>maid</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -17322,75 +17322,875 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>magical princess</t>
+          <t>etoile</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>453</v>
+        <v>56</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Demi Lich</t>
+          <t>Himiko</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834 (Hentaicheg), Best in Slot Gear + Sealbooks: Demi Lich (level 69), "a pretty early sealbook", for the Diva and offensive mages</t>
+          <t>GameFAQs faqs/80834 (Hentaicheg), Best in Slot Gear + Sealbooks: Himiko (level 81, a regular monster), top tier for the Etoile</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>maid</t>
+          <t>soul summoner</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>453</v>
+        <v>90</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Demi Lich</t>
+          <t>Ainsel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834 (Hentaicheg), Best in Slot Gear + Sealbooks: Demi Lich (level 69), "a pretty early sealbook", for the Diva and offensive mages</t>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>etoile</t>
+          <t>dolls</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Himiko</t>
+          <t>Ainsel</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P16</t>
+          <t>C02</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GameFAQs faqs/80834 (Hentaicheg), Best in Slot Gear + Sealbooks: Himiko (level 81, a regular monster), top tier for the Etoile</t>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>84</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Spider Girl</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>84</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Spider Girl</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>C03</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>823</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Bigtooth</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>823</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Bigtooth</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>C07</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>342</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Creature</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>342</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Creature</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>C08</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>743</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Selene</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>743</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Selene</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>C09</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>193</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Eel</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>193</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Eel</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>772</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Korpokkur</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>772</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Korpokkur</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>141</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>141</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Demon</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>433</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Skull Collector</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>433</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Skull Collector</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>C18</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>715</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Psycher</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>715</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Psycher</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>845</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ape</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>845</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ape</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>C24</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>393</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Dragonkin</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>393</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Dragonkin</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>C25</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>101</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>C27</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>101</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Kraken</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>C27</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>182</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Momunofu</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>182</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Momunofu</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>C28</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>891</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Gargouille</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>891</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Gargouille</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>C29</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>910</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Overlord</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>910</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Overlord</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Derived: the strongest regular enemy (stat sum) of the floors reached before the checkpoint; a sealbook a player carries for Soul Seal</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>soul summoner</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>458</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Persephone</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>GameFAQs faqs/80834 (Hentaicheg), Best in Slot Gear + Sealbooks: Persephone (level 66, sealed in the first postgame dungeon), "can get it early and it is pretty solid forever" for physical roles</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>458</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Persephone</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>P06</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>GameFAQs faqs/80834 (Hentaicheg), Best in Slot Gear + Sealbooks: Persephone (level 66, sealed in the first postgame dungeon), "can get it early and it is pretty solid forever" for physical roles</t>
         </is>
       </c>
     </row>
@@ -23007,7 +23807,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Spartan; Catalina; Doll Mastery; Double Puppet; Mercidarian; Perdurabo; Musiy; Soul Eater; Oracles; Destiny Line; Coffee Break; Weapon Mastery; Danger Shoot</t>
+          <t>Spartan; Catalina; Doll Mastery; Double Puppet; Soul Seal; Mercidarian; Perdurabo; Musiy; Soul Eater; Oracles; Destiny Line; Coffee Break; Weapon Mastery; Danger Shoot</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -20482,7 +20482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22866,6 +22866,56 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>the class kit: Divine Shield (skill 201) of the Priestess line, prebuffed in hard fights as the other support roles prebuff their guards (2026-10-19: the role never cast it; class-search showed her parties the lowest of the lowest HP from C27 on)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>dolls</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>party_hp_below:0.6</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>skill:Catalina</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>skill-rule-trial of 2026-10-29 (16 bosses, 1000 battles each): Catalina summoned every time TP allowed cost the party 9 casts of 48 TP a battle (fights 16% longer, 6 of 16 bosses worse); summoned when the party is below 60% HP: wins +1.2 points, fights 0.9% longer, 0 bosses worse, 3 better by 3 points or more</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>attacker</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>turn_at_most:3</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>skill:Armor Penetration</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>skill-rule-trial of 2026-10-29 (16 bosses, 1000 battles each): the policy never chose it (38 - 44% of the damage per time of Moonlight Purgatory) but its DEF -24% to -38% for 4 turns serves the whole party; cast once at the start of a fight: wins +0.3 points, fights 1.5% shorter, 4 bosses served and 1 hurt, against 5 hurt when it is used every time</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -20482,7 +20482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22916,6 +22916,31 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>skill-rule-trial of 2026-10-29 (16 bosses, 1000 battles each): the policy never chose it (38 - 44% of the damage per time of Moonlight Purgatory) but its DEF -24% to -38% for 4 turns serves the whole party; cast once at the start of a fight: wins +0.3 points, fights 1.5% shorter, 4 bosses served and 1 hurt, against 5 hurt when it is used every time</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>shooter</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>always</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>status:191</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>one-skill-trial of 2026-10-29 (16 bosses, 1000 battles each): Aim kept up as the archer lines use it (atwiki dt2-2 pages 127, 140); with its damage bonus +10% to +30% it shortens the won fights 7.3% and hurts none of the 16 bosses</t>
         </is>
       </c>
     </row>

--- a/data_tables/sim_setup.xlsx
+++ b/data_tables/sim_setup.xlsx
@@ -22190,7 +22190,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>atwiki dt2-2 page 122: the Paladin uses herself as the shield of the party (Protect kept up on the weakest member)</t>
+          <t>atwiki dt2-2 page 122: the Paladin uses herself as the shield of the party (Protect kept up on herself while Provoke is up); the spell adds a share of the DEF of its target, so otherwise it goes on the ally with the highest DEF</t>
         </is>
       </c>
     </row>
